--- a/reports/Debug-purgatory-20260105/For Winter Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260105/For Winter Ending (Prior Year)_Revenue.xlsx
@@ -118,16 +118,16 @@
     <t>T103</t>
   </si>
   <si>
+    <t>T101</t>
+  </si>
+  <si>
     <t>T104</t>
   </si>
   <si>
-    <t>T101</t>
+    <t>T105</t>
   </si>
   <si>
     <t>T100</t>
-  </si>
-  <si>
-    <t>T105</t>
   </si>
   <si>
     <t>department</t>
@@ -589,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -612,11 +612,17 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="D2" s="2">
-        <v>780.00</v>
+        <v>300.00</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -624,27 +630,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="2">
-        <v>40395.00</v>
+        <v>308470.93</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="2">
-        <v>2339.47</v>
+        <v>1263.50</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -658,7 +662,7 @@
         <v>39</v>
       </c>
       <c r="D5" s="2">
-        <v>2241436.83</v>
+        <v>945.30</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -672,7 +676,7 @@
         <v>39</v>
       </c>
       <c r="D6" s="2">
-        <v>3292776.61</v>
+        <v>8526.00</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -686,378 +690,366 @@
         <v>39</v>
       </c>
       <c r="D7" s="2">
-        <v>36076.00</v>
+        <v>1243594.64</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2">
-        <v>1263.50</v>
+        <v>811148.97</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="2">
-        <v>870860.21</v>
+        <v>23600.00</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2">
-        <v>23600.00</v>
+        <v>911183.14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2">
-        <v>970120.10</v>
+        <v>2.00</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2">
-        <v>2.00</v>
+        <v>95672.48</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="2">
-        <v>99692.89</v>
+        <v>492093.20</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2">
-        <v>518349.15</v>
+        <v>179889.50</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" s="2">
-        <v>187317.26</v>
+        <v>133452.89</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="2">
-        <v>144373.83</v>
+        <v>173710.76</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="2">
-        <v>203239.07</v>
+        <v>189607.02</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2">
-        <v>220034.99</v>
+        <v>22837.25</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="2">
-        <v>25782.50</v>
+        <v>23247.20</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2">
-        <v>47501.04</v>
+        <v>102697.36</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" s="2">
-        <v>123037.64</v>
+        <v>520135.87</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="2">
-        <v>620470.55</v>
+        <v>72679.66</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23" s="2">
-        <v>92274.43</v>
+        <v>48830.00</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D24" s="2">
-        <v>48830.00</v>
+        <v>300.00</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D25" s="2">
-        <v>300.00</v>
+        <v>1587998.16</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D26" s="2">
-        <v>1629400.07</v>
+        <v>70383.73</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2">
-        <v>140223.73</v>
+        <v>77965.68</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D28" s="2">
-        <v>86247.33</v>
+        <v>281486.03</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D29" s="2">
-        <v>428459.00</v>
+        <v>7661.72</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D30" s="2">
-        <v>20872.97</v>
+        <v>38781.42</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D31" s="2">
-        <v>58875.27</v>
+        <v>99542.20</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D32" s="2">
-        <v>191589.64</v>
+        <v>78000.43</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D33" s="2">
-        <v>124610.64</v>
+        <v>39592.90</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D34" s="2">
-        <v>127444.17</v>
+        <v>4916.98</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D35" s="2">
-        <v>21475.45</v>
+        <v>8000.00</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D36" s="2">
-        <v>8000.00</v>
+        <v>96377.53</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D37" s="2">
-        <v>109670.58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" s="2">
         <v>1364.14</v>
       </c>
     </row>
